--- a/实验三_DevOps流水线与容器化部署/D3-7_DORA指标报告.xlsx
+++ b/实验三_DevOps流水线与容器化部署/D3-7_DORA指标报告.xlsx
@@ -7,9 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原始数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周度汇总" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="趋势图说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="指标概览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原始数据" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周度汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="趋势图说明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改进计划" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="趋势图" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +40,17 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F6B45"/>
+      <sz val="16"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,8 +67,13 @@
         <fgColor rgb="00F2F8F4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F6B45"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -78,11 +95,25 @@
         <color rgb="00B8D8C2"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C9BF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7C9BF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7C9BF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7C9BF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +130,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -173,6 +211,565 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>部署频率趋势</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'原始数据'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'原始数据'!$A$2:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'原始数据'!$B$2:$B$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>日期</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>部署次数</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>变更前置时间趋势</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'原始数据'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'原始数据'!$A$2:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'原始数据'!$C$2:$C$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>日期</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>小时</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>当日变更失败率</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'原始数据'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'原始数据'!$A$2:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'原始数据'!$G$2:$G$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>日期</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>%</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>MTTR 趋势</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'原始数据'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'原始数据'!$A$2:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'原始数据'!$E$2:$E$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>日期</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>分钟</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,266 +1061,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>部署次数</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>变更前置时间(小时)</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>变更失败次数</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>MTTR(分钟)</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>初始化 PoC</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>补单元测试</t>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>当前值</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>目标阈值</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>评级</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>日均部署次数</t>
+        </is>
+      </c>
+      <c r="B2" s="7">
+        <f>ROUND(AVERAGE('原始数据'!B2:B10),2)</f>
+        <v/>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>&gt;=1 次/日</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>实验期保持高频小步交付</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>中位前置时间(小时)</t>
+        </is>
+      </c>
+      <c r="B3" s="7">
+        <f>MEDIAN('原始数据'!C2:C10)</f>
+        <v/>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=4 小时</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>从提交到可部署版本的等待时间较短</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>修复 Dockerfile</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>变更失败率(%)</t>
+        </is>
+      </c>
+      <c r="B4" s="7">
+        <f>ROUND(SUM('原始数据'!D2:D10)/SUM('原始数据'!B2:B10)*100,2)</f>
+        <v/>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=15%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>失败变更占总部署次数比例</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Compose 起栈</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>平均 MTTR(分钟)</t>
+        </is>
+      </c>
+      <c r="B5" s="7">
+        <f>ROUND(AVERAGEIF('原始数据'!E2:E10,"&gt;0",'原始数据'!E2:E10),2)</f>
+        <v/>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=30 分钟</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>失败后恢复耗时，未失败日期不计入平均</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>CI 缓存</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>综合结论</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>持续改进</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>达标</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>当前 PoC 已具备较快交付、较低失败率和可恢复能力</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Helm values</t>
-        </is>
-      </c>
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>回滚演练</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>报告说明</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>本报告基于实验三 CI/CD、镜像扫描、Compose 起栈、Helm 发布和可观测演练数据整理，用于衡量 NekoCafé DevOps PoC 的交付效率与恢复能力。</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>观测面板</t>
-        </is>
-      </c>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>分析结论</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>部署频率稳定在每日多次，前置时间从 5 小时逐步降低到 2 小时，变更失败率低于 15%，MTTR 低于 30 分钟，说明当前流水线具备 High 级别的实验交付成熟度。</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>基线冻结</t>
-        </is>
-      </c>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>后续关注</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>继续补充端到端测试、契约测试、自动回滚指标和发布后复盘记录，避免 PoC 阶段的手工演练在真实项目中变成不可追溯操作。</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B8:E8"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -734,95 +1297,347 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>周次</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>日均部署次数</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>中位前置时间(小时)</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>变更失败率(%)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>平均MTTR(分钟)</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>DORA 等级</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>部署次数</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>变更前置时间(小时)</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>变更失败次数</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>MTTR(分钟)</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>当日变更失败率(%)</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>是否触发复盘</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>W19</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>初始化 PoC</t>
+        </is>
+      </c>
+      <c r="G2" s="7">
+        <f>IF(B2=0,0,D2/B2*100)</f>
+        <v/>
+      </c>
+      <c r="H2" s="7">
+        <f>IF(OR(D2&gt;0,E2&gt;0),"是","否")</f>
+        <v/>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>W20</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>补单元测试</t>
+        </is>
+      </c>
+      <c r="G3" s="7">
+        <f>IF(B3=0,0,D3/B3*100)</f>
+        <v/>
+      </c>
+      <c r="H3" s="7">
+        <f>IF(OR(D3&gt;0,E3&gt;0),"是","否")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="C4" s="7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>修复 Dockerfile</t>
+        </is>
+      </c>
+      <c r="G4" s="7">
+        <f>IF(B4=0,0,D4/B4*100)</f>
+        <v/>
+      </c>
+      <c r="H4" s="7">
+        <f>IF(OR(D4&gt;0,E4&gt;0),"是","否")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Compose 起栈</t>
+        </is>
+      </c>
+      <c r="G5" s="7">
+        <f>IF(B5=0,0,D5/B5*100)</f>
+        <v/>
+      </c>
+      <c r="H5" s="7">
+        <f>IF(OR(D5&gt;0,E5&gt;0),"是","否")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>CI 缓存</t>
+        </is>
+      </c>
+      <c r="G6" s="7">
+        <f>IF(B6=0,0,D6/B6*100)</f>
+        <v/>
+      </c>
+      <c r="H6" s="7">
+        <f>IF(OR(D6&gt;0,E6&gt;0),"是","否")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Helm values</t>
+        </is>
+      </c>
+      <c r="G7" s="7">
+        <f>IF(B7=0,0,D7/B7*100)</f>
+        <v/>
+      </c>
+      <c r="H7" s="7">
+        <f>IF(OR(D7&gt;0,E7&gt;0),"是","否")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>回滚演练</t>
+        </is>
+      </c>
+      <c r="G8" s="7">
+        <f>IF(B8=0,0,D8/B8*100)</f>
+        <v/>
+      </c>
+      <c r="H8" s="7">
+        <f>IF(OR(D8&gt;0,E8&gt;0),"是","否")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>观测面板</t>
+        </is>
+      </c>
+      <c r="G9" s="7">
+        <f>IF(B9=0,0,D9/B9*100)</f>
+        <v/>
+      </c>
+      <c r="H9" s="7">
+        <f>IF(OR(D9&gt;0,E9&gt;0),"是","否")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>基线冻结</t>
+        </is>
+      </c>
+      <c r="G10" s="7">
+        <f>IF(B10=0,0,D10/B10*100)</f>
+        <v/>
+      </c>
+      <c r="H10" s="7">
+        <f>IF(OR(D10&gt;0,E10&gt;0),"是","否")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -836,152 +1651,587 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>周次</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>日均部署次数</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>中位前置时间(小时)</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>变更失败率(%)</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>平均MTTR(分钟)</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>DORA 等级</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>主要观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="B2" s="7">
+        <f>ROUND(AVERAGE('原始数据'!B2:B6),2)</f>
+        <v/>
+      </c>
+      <c r="C2" s="7">
+        <f>MEDIAN('原始数据'!C2:C6)</f>
+        <v/>
+      </c>
+      <c r="D2" s="7">
+        <f>ROUND(SUM('原始数据'!D2:D6)/SUM('原始数据'!B2:B6)*100,2)</f>
+        <v/>
+      </c>
+      <c r="E2" s="7">
+        <f>ROUND(AVERAGEIF('原始数据'!E2:E6,"&gt;0",'原始数据'!E2:E6),2)</f>
+        <v/>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>完成 PoC 初始化、测试补充、Dockerfile 修复和 Compose 起栈</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="B3" s="7">
+        <f>ROUND(AVERAGE('原始数据'!B7:B10),2)</f>
+        <v/>
+      </c>
+      <c r="C3" s="7">
+        <f>MEDIAN('原始数据'!C7:C10)</f>
+        <v/>
+      </c>
+      <c r="D3" s="7">
+        <f>ROUND(SUM('原始数据'!D7:D10)/SUM('原始数据'!B7:B10)*100,2)</f>
+        <v/>
+      </c>
+      <c r="E3" s="7">
+        <f>ROUND(AVERAGEIF('原始数据'!E7:E10,"&gt;0",'原始数据'!E7:E10),2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>完成 Helm values、回滚演练、观测面板和基线冻结</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>总体</t>
+        </is>
+      </c>
+      <c r="B4" s="7">
+        <f>ROUND(AVERAGE('原始数据'!B2:B10),2)</f>
+        <v/>
+      </c>
+      <c r="C4" s="7">
+        <f>MEDIAN('原始数据'!C2:C10)</f>
+        <v/>
+      </c>
+      <c r="D4" s="7">
+        <f>ROUND(SUM('原始数据'!D2:D10)/SUM('原始数据'!B2:B10)*100,2)</f>
+        <v/>
+      </c>
+      <c r="E4" s="7">
+        <f>ROUND(AVERAGEIF('原始数据'!E2:E10,"&gt;0",'原始数据'!E2:E10),2)</f>
+        <v/>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>整体达到高频交付、低失败率和快速恢复目标</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>图编号</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>位置</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>生成方式</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>分析说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>F-1</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>部署频率趋势</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>周度汇总!B:B</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>原始数据!A:B</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>折线图</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>目标：日均 ≥ 1 次</t>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>观察实验期每日部署次数，目标为日均不少于 1 次</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>F-2</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>前置时间趋势</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>周度汇总!C:C</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>原始数据!A:C</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>折线图</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>目标：中位数 ≤ 4 小时</t>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>观察提交到可部署版本的等待时间是否持续下降</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>F-3</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>变更失败率</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>周度汇总!D:D</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>原始数据!A:G</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>柱状图</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>目标：≤ 15%</t>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>观察失败变更占比是否低于 15%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>F-4</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>MTTR</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>周度汇总!E:E</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>原始数据!A:E</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>折线图</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>目标：≤ 30 分钟</t>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>观察失败后恢复耗时是否低于 30 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>F-5</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>周度成熟度</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>周度汇总!A:F</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>表格/柱状图</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>对比 W19/W20 的 DORA 等级和主要改进方向</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>改进项</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>关联指标</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>当前问题</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>改进动作</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>补充契约测试</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>变更失败率</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>接口边界变化可能只在部署后暴露</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>为 reservation/member 关键接口增加契约测试</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>PR 阶段即可发现接口字段不兼容</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>完善发布后自动检查</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>MTTR</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>CD 仍依赖人工观察部分指标</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>在 CD 中查询 Prometheus P95/错误率并输出摘要</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>异常时自动阻断或回滚</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>增加端到端冒烟测试</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>前置时间/失败率</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>单元测试不能覆盖跨服务链路</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Compose 起栈后执行预约创建与会员查询脚本</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>流水线产出可复现冒烟测试日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>沉淀故障复盘模板</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>MTTR</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>失败处理记录不够标准化</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>记录触发时间、根因、恢复动作和预防措施</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>每次失败变更都有复盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>引入 SBOM 和镜像签名</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>安全质量</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>供应链证据仍偏手工</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>生成 SBOM 并探索 cosign 签名</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>镜像交付附带物料清单和签名信息</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>NekoCafé DevOps DORA 趋势图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>图表基于“原始数据”和“周度汇总”生成，用于展示部署频率、前置时间、失败率和 MTTR 的变化趋势。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>